--- a/Application/SQL/gomibunbetsujiten.xlsx
+++ b/Application/SQL/gomibunbetsujiten.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="５０音順" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="５０音順" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -752,7 +752,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -873,7 +878,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -965,7 +975,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1028,7 +1043,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1381,7 +1401,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2344,7 +2369,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3336,7 +3366,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>購入店へ返却または資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>購入店へ返却または（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3399,7 +3434,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3428,7 +3468,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -4057,12 +4102,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>金紙、銀紙は「可燃ごみ」へ</t>
+          <t>（古紙・布類）の【古紙（雑がみ）】金紙、銀紙は「可燃ごみ」へ</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4473,12 +4518,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（紙パック）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>水ですすいで乾かしてからひもで十文字に束ねる</t>
+          <t>（古紙・布類）の【古紙（紙パック）】水ですすいで乾かしてからひもで十文字に束ねる</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -5600,7 +5645,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5697,12 +5747,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>・可燃ごみで出す場合は、ひもで束ねて、1回に出す量は片手で持てる量で3束程度排出可。・資源物（木の枝・刈草・葉）の収集日は、片手で持てる量でひもで束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）</t>
+          <t>（木の枝・刈り草・葉）・可燃ごみで出す場合は、ひもで束ねて、1回に出す量は片手で持てる量で3束程度排出可。・資源物（木の枝・刈草・葉）の収集日は、片手で持てる量でひもで束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5799,12 +5849,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>・ひもで片手で持てる重さまでに束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・太さや長さがこれを超える場合は、千葉市廃棄物リサイクル事業協同組合（電話043-204-5805）へご相談ください。</t>
+          <t>（木の枝・刈り草・葉）・ひもで片手で持てる重さまでに束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・太さや長さがこれを超える場合は、千葉市廃棄物リサイクル事業協同組合（電話043-204-5805）へご相談ください。</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -6641,7 +6691,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -6733,12 +6788,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>http://www.city.chiba.jp/kankyo/junkan/shushugyomu/syusyushinai.html／http://www.city.chiba.jp/kankyo/junkan/shushugyomu/syusyushinai.html</t>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】http://www.city.chiba.jp/kankyo/junkan/shushugyomu/syusyushinai.html／http://www.city.chiba.jp/kankyo/junkan/shushugyomu/syusyushinai.html</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -6956,7 +7011,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -7222,12 +7282,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
+          <t>（木の枝・刈り草・葉）・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -7619,7 +7679,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F239" t="n">
@@ -7677,7 +7742,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F241" t="n">
@@ -7735,7 +7805,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（新聞）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（新聞）】</t>
         </is>
       </c>
       <c r="F243" t="n">
@@ -8088,7 +8163,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -8146,7 +8226,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F257" t="n">
@@ -8204,7 +8289,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -9714,7 +9804,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -9772,7 +9867,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -9801,7 +9901,12 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -10618,7 +10723,12 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -11600,7 +11710,12 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -11832,12 +11947,12 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（紙パック）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>水ですすいで乾かしてからひもで十文字に束ねる</t>
+          <t>（古紙・布類）の【古紙（紙パック）】水ですすいで乾かしてからひもで十文字に束ねる</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -11924,7 +12039,12 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -12103,12 +12223,12 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>http://www.city.chiba.jp/kankyo/junkan/haikibutsu/haisyokuyu.html／http://www.city.chiba.jp/kankyo/junkan/haikibutsu/haisyokuyu.html</t>
+          <t>（古紙・布類）の【古紙（雑がみ）】http://www.city.chiba.jp/kankyo/junkan/haikibutsu/haisyokuyu.html／http://www.city.chiba.jp/kankyo/junkan/haikibutsu/haisyokuyu.html</t>
         </is>
       </c>
       <c r="F390" t="n">
@@ -12287,7 +12407,12 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -12645,12 +12770,12 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
+          <t>（木の枝・刈り草・葉）・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -12800,12 +12925,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
+          <t>（木の枝・刈り草・葉）・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
         </is>
       </c>
       <c r="F413" t="n">
@@ -12868,12 +12993,12 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>金属部分は取り外して不燃ごみへ</t>
+          <t>（古紙・布類）の【古紙（雑がみ）】金属部分は取り外して不燃ごみへ</t>
         </is>
       </c>
       <c r="F415" t="n">
@@ -13023,7 +13148,12 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -13115,7 +13245,12 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F423" t="n">
@@ -13647,7 +13782,12 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F441" t="n">
@@ -13676,12 +13816,12 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>・可燃ごみで出す場合は、ひもで束ねて、1回に出す量は片手で持てる量で3束程度排出可。・資源物（木の枝・刈草・葉）の収集日は、片手で持てる量でひもで束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）</t>
+          <t>（木の枝・刈り草・葉）・可燃ごみで出す場合は、ひもで束ねて、1回に出す量は片手で持てる量で3束程度排出可。・資源物（木の枝・刈草・葉）の収集日は、片手で持てる量でひもで束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）</t>
         </is>
       </c>
       <c r="F442" t="n">
@@ -13778,12 +13918,12 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>・ひもで片手で持てる重さまでに束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・太さや長さがこれを超える場合は、千葉市廃棄物リサイクル事業協同組合（電話043-204-5805）へご相談ください。</t>
+          <t>（木の枝・刈り草・葉）・ひもで片手で持てる重さまでに束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・太さや長さがこれを超える場合は、千葉市廃棄物リサイクル事業協同組合（電話043-204-5805）へご相談ください。</t>
         </is>
       </c>
       <c r="F445" t="n">
@@ -14499,7 +14639,12 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -14591,12 +14736,12 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>http://www.jbrc.com/／http://www.jbrc.com/</t>
+          <t>（古紙・布類）の【古紙（雑がみ）】http://www.jbrc.com/／http://www.jbrc.com/</t>
         </is>
       </c>
       <c r="F472" t="n">
@@ -14833,12 +14978,12 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（紙パック）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>水ですすいで乾かしてからひもで十文字に束ねる</t>
+          <t>（古紙・布類）の【古紙（紙パック）】水ですすいで乾かしてからひもで十文字に束ねる</t>
         </is>
       </c>
       <c r="F480" t="n">
@@ -14867,7 +15012,12 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -15046,7 +15196,12 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F487" t="n">
@@ -15704,7 +15859,12 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>（木の枝・刈り草・葉）</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -16062,7 +16222,12 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F521" t="n">
@@ -16149,7 +16314,12 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F524" t="n">
@@ -16323,7 +16493,12 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F530" t="n">
@@ -16352,7 +16527,12 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（段ボール）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（段ボール）】</t>
         </is>
       </c>
       <c r="F531" t="n">
@@ -16555,7 +16735,12 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -16739,7 +16924,12 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F544" t="n">
@@ -16768,7 +16958,12 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（段ボール）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（段ボール）】</t>
         </is>
       </c>
       <c r="F545" t="n">
@@ -17532,7 +17727,12 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（段ボール）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（段ボール）】</t>
         </is>
       </c>
       <c r="F571" t="n">
@@ -18481,7 +18681,12 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -18544,7 +18749,12 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -18689,12 +18899,12 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>https://www.city.chiba.jp/kankyo/junkan/shushugyomu/hinmoku-kakudai.html</t>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】https://www.city.chiba.jp/kankyo/junkan/shushugyomu/hinmoku-kakudai.html</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -18965,7 +19175,12 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -19241,7 +19456,12 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F627" t="n">
@@ -19391,7 +19611,12 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F632" t="n">
@@ -19420,7 +19645,12 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F633" t="n">
@@ -19449,7 +19679,12 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F634" t="n">
@@ -19623,7 +19858,12 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F640" t="n">
@@ -19739,7 +19979,12 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="F644" t="n">
@@ -19797,7 +20042,12 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -20218,7 +20468,12 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -20310,7 +20565,12 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F663" t="n">
@@ -20426,7 +20686,12 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F667" t="n">
@@ -20455,12 +20720,12 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
+          <t>（木の枝・刈り草・葉）・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
         </is>
       </c>
       <c r="F668" t="n">
@@ -20644,7 +20909,12 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（新聞）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（新聞）】</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -20678,7 +20948,12 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F675" t="n">
@@ -21128,7 +21403,12 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F690" t="n">
@@ -21186,7 +21466,12 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（段ボール）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（段ボール）】</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
@@ -21723,7 +22008,12 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -22478,7 +22768,12 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -22512,7 +22807,12 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
@@ -22546,7 +22846,12 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F737" t="n">
@@ -22604,7 +22909,12 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（紙パック）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（紙パック）】</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
@@ -22638,7 +22948,12 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -22759,7 +23074,12 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F744" t="n">
@@ -22788,7 +23108,12 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
         </is>
       </c>
       <c r="F745" t="n">
@@ -22914,7 +23239,12 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
@@ -23311,7 +23641,12 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
@@ -23374,7 +23709,12 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
@@ -23558,7 +23898,12 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F770" t="n">
@@ -24066,7 +24411,12 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F787" t="n">
@@ -24269,7 +24619,12 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F794" t="n">
@@ -24506,7 +24861,12 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F802" t="n">
@@ -25203,7 +25563,12 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
@@ -25266,7 +25631,12 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
@@ -25474,7 +25844,12 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F834" t="n">
@@ -25561,7 +25936,12 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
@@ -25595,7 +25975,12 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
@@ -25692,7 +26077,12 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
@@ -25755,12 +26145,12 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（紙パック）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>水ですすいで乾かしてからひもで十文字に束ねる</t>
+          <t>（古紙・布類）の【古紙（紙パック）】水ですすいで乾かしてからひもで十文字に束ねる</t>
         </is>
       </c>
       <c r="F843" t="n">
@@ -26534,7 +26924,12 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
@@ -26568,7 +26963,12 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
@@ -26665,7 +27065,12 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -26835,7 +27240,12 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
@@ -26869,12 +27279,12 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>https://www.tca.or.jp/mobile-recycle/</t>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】https://www.tca.or.jp/mobile-recycle/</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
@@ -27537,7 +27947,12 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（新聞）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（新聞）】</t>
         </is>
       </c>
       <c r="F901" t="n">
@@ -27566,7 +27981,12 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
@@ -27808,7 +28228,12 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F910" t="n">
@@ -27900,7 +28325,12 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F913" t="n">
@@ -28514,7 +28944,12 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -28867,7 +29302,12 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F946" t="n">
@@ -29675,7 +30115,12 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F973" t="n">
@@ -30231,7 +30676,12 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E992" t="inlineStr">
@@ -30265,7 +30715,12 @@
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
@@ -30299,7 +30754,12 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
@@ -30391,7 +30851,12 @@
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F997" t="n">
@@ -30715,7 +31180,12 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1008" t="n">
@@ -30773,7 +31243,12 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F1010" t="n">
@@ -30865,7 +31340,12 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F1013" t="n">
@@ -30981,7 +31461,12 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1017" t="n">
@@ -31126,7 +31611,12 @@
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1022" t="n">
@@ -31914,12 +32404,12 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
-          <t>・可燃ごみで出す場合は、ひもで束ねて、1回に出す量は片手で持てる量で3束程度排出可。・資源物（木の枝・刈草・葉）の収集日は、片手で持てる量でひもで束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）</t>
+          <t>（木の枝・刈り草・葉）・可燃ごみで出す場合は、ひもで束ねて、1回に出す量は片手で持てる量で3束程度排出可。・資源物（木の枝・刈草・葉）の収集日は、片手で持てる量でひもで束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）</t>
         </is>
       </c>
       <c r="F1049" t="n">
@@ -32016,12 +32506,12 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>・ひもで片手で持てる重さまでに束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・太さや長さがこれを超える場合は、千葉市廃棄物リサイクル事業協同組合（電話043-204-5805）へご相談ください。</t>
+          <t>（木の枝・刈り草・葉）・ひもで片手で持てる重さまでに束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・太さや長さがこれを超える場合は、千葉市廃棄物リサイクル事業協同組合（電話043-204-5805）へご相談ください。</t>
         </is>
       </c>
       <c r="F1052" t="n">
@@ -32505,7 +32995,12 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1068" t="n">
@@ -32592,7 +33087,12 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="F1071" t="n">
@@ -33173,7 +33673,12 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1090" t="n">
@@ -33594,7 +34099,12 @@
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1104" t="n">
@@ -33865,7 +34375,12 @@
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1113" t="n">
@@ -33923,7 +34438,12 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>（木の枝・刈り草・葉）</t>
         </is>
       </c>
       <c r="E1115" t="inlineStr">
@@ -34025,12 +34545,12 @@
       </c>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1118" t="inlineStr">
         <is>
-          <t>・ひもで片手で持てる重さまでに束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・太さや長さがこれを超える場合は、千葉市廃棄物リサイクル事業協同組合（電話043-204-5805）へご相談ください。</t>
+          <t>（木の枝・刈り草・葉）・ひもで片手で持てる重さまでに束ねる。指定袋に入れなくても可。何束でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・太さや長さがこれを超える場合は、千葉市廃棄物リサイクル事業協同組合（電話043-204-5805）へご相談ください。</t>
         </is>
       </c>
       <c r="F1118" t="n">
@@ -34533,7 +35053,12 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1135" t="n">
@@ -34746,7 +35271,12 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E1142" t="inlineStr">
@@ -34867,7 +35397,12 @@
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F1146" t="n">
@@ -35041,12 +35576,12 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（段ボール）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
         <is>
-          <t>1枚でも必ずたたんでからひもで束ねる</t>
+          <t>（古紙・布類）の【古紙（段ボール）】1枚でも必ずたたんでからひもで束ねる</t>
         </is>
       </c>
       <c r="F1152" t="n">
@@ -35486,7 +36021,12 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F1167" t="n">
@@ -35544,7 +36084,12 @@
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1169" t="n">
@@ -35573,7 +36118,12 @@
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（段ボール）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（段ボール）】</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
@@ -35607,7 +36157,12 @@
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F1171" t="n">
@@ -36067,7 +36622,12 @@
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E1186" t="inlineStr">
@@ -36101,7 +36661,12 @@
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E1187" t="inlineStr">
@@ -36280,7 +36845,12 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1193" t="n">
@@ -36981,7 +37551,12 @@
       </c>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
         </is>
       </c>
       <c r="E1217" t="inlineStr">
@@ -37015,7 +37590,12 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E1218" t="inlineStr">
@@ -37349,7 +37929,12 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F1229" t="n">
@@ -37470,7 +38055,12 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1233" t="n">
@@ -37828,7 +38418,12 @@
       </c>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1245" t="n">
@@ -37915,7 +38510,12 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="E1248" t="inlineStr">
@@ -38017,7 +38617,12 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="E1251" t="inlineStr">
@@ -38574,7 +39179,12 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（段ボール）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（段ボール）】</t>
         </is>
       </c>
       <c r="F1269" t="n">
@@ -39010,7 +39620,12 @@
       </c>
       <c r="C1283" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F1283" t="n">
@@ -40252,12 +40867,12 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1321" t="inlineStr">
         <is>
-          <t>https://www.city.chiba.jp/kankyo/junkan/shushugyomu/hinmoku-kakudai.html／https://www.city.chiba.jp/kankyo/junkan/shushugyomu/hinmoku-kakudai.html</t>
+          <t>（古紙・布類）の【古紙（雑誌）】https://www.city.chiba.jp/kankyo/junkan/shushugyomu/hinmoku-kakudai.html／https://www.city.chiba.jp/kankyo/junkan/shushugyomu/hinmoku-kakudai.html</t>
         </is>
       </c>
       <c r="F1321" t="n">
@@ -40441,7 +41056,12 @@
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1327" t="n">
@@ -41608,7 +42228,12 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F1365" t="n">
@@ -41695,7 +42320,12 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E1368" t="inlineStr">
@@ -43083,7 +43713,12 @@
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F1415" t="n">
@@ -43272,12 +43907,12 @@
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1421" t="inlineStr">
         <is>
-          <t>http://www.jbrc.com/</t>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】http://www.jbrc.com/</t>
         </is>
       </c>
       <c r="E1421" t="inlineStr">
@@ -43311,12 +43946,12 @@
       </c>
       <c r="C1422" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1422" t="inlineStr">
         <is>
-          <t>https://www.city.chiba.jp/kankyo/junkan/shushugyomu/hinmoku-kakudai.html／https://www.city.chiba.jp/kankyo/junkan/shushugyomu/hinmoku-kakudai.html</t>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】https://www.city.chiba.jp/kankyo/junkan/shushugyomu/hinmoku-kakudai.html／https://www.city.chiba.jp/kankyo/junkan/shushugyomu/hinmoku-kakudai.html</t>
         </is>
       </c>
       <c r="F1422" t="n">
@@ -43345,7 +43980,12 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F1423" t="n">
@@ -43374,12 +44014,12 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1424" t="inlineStr">
         <is>
-          <t>・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
+          <t>（木の枝・刈り草・葉）・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
         </is>
       </c>
       <c r="F1424" t="n">
@@ -43994,7 +44634,12 @@
       </c>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="E1444" t="inlineStr">
@@ -44415,7 +45060,12 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="E1458" t="inlineStr">
@@ -44812,12 +45462,12 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1471" t="inlineStr">
         <is>
-          <t>http://www.city.chiba.jp/kankyo/junkan/haikibutsu/haisyokuyu.html／http://www.city.chiba.jp/kankyo/junkan/haikibutsu/haisyokuyu.html</t>
+          <t>（古紙・布類）の【古紙（雑がみ）】http://www.city.chiba.jp/kankyo/junkan/haikibutsu/haisyokuyu.html／http://www.city.chiba.jp/kankyo/junkan/haikibutsu/haisyokuyu.html</t>
         </is>
       </c>
       <c r="F1471" t="n">
@@ -45233,12 +45883,12 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
         <is>
-          <t>・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
+          <t>（木の枝・刈り草・葉）・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
         </is>
       </c>
       <c r="F1485" t="n">
@@ -45301,12 +45951,12 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>資源物（木の枝・刈り草・葉）</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr">
         <is>
-          <t>・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
+          <t>（木の枝・刈り草・葉）・可燃・不燃ごみ旧指定袋を含む、透明・半透明袋で排出できます。何袋でも排出可。（ごみステーションからあふれる場合など多量になるときは、分けて排出してください。）・1回につき3袋程度までであれば、可燃ごみでも排出可</t>
         </is>
       </c>
       <c r="F1487" t="n">
@@ -45490,7 +46140,12 @@
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1493" t="n">
@@ -46501,7 +47156,12 @@
       </c>
       <c r="C1527" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1527" t="n">
@@ -46864,7 +47524,12 @@
       </c>
       <c r="C1539" t="inlineStr">
         <is>
-          <t>購入店へ返却または資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>購入店へ返却または（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E1539" t="inlineStr">
@@ -46898,7 +47563,12 @@
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F1540" t="n">
@@ -46927,7 +47597,12 @@
       </c>
       <c r="C1541" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E1541" t="inlineStr">
@@ -47619,7 +48294,12 @@
       </c>
       <c r="C1564" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="E1564" t="inlineStr">
@@ -47653,12 +48333,12 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1565" t="inlineStr">
         <is>
-          <t>事典とは別にし、たたんでひもで十文字にしばる。</t>
+          <t>（古紙・布類）の【古紙（雑がみ）】事典とは別にし、たたんでひもで十文字にしばる。</t>
         </is>
       </c>
       <c r="F1565" t="n">
@@ -47716,7 +48396,12 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E1567" t="inlineStr">
@@ -47784,7 +48469,12 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F1569" t="n">
@@ -47929,7 +48619,12 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="E1574" t="inlineStr">
@@ -48031,7 +48726,12 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1577" t="n">
@@ -48205,12 +48905,12 @@
       </c>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1583" t="inlineStr">
         <is>
-          <t>http://www.city.chiba.jp/kankyo/junkan/shushugyomu/syusyushinai.html／http://www.city.chiba.jp/kankyo/junkan/shushugyomu/syusyushinai.html</t>
+          <t>（古紙・布類）の【古紙（雑がみ）】http://www.city.chiba.jp/kankyo/junkan/shushugyomu/syusyushinai.html／http://www.city.chiba.jp/kankyo/junkan/shushugyomu/syusyushinai.html</t>
         </is>
       </c>
       <c r="F1583" t="n">
@@ -48413,7 +49113,12 @@
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="E1590" t="inlineStr">
@@ -48539,7 +49244,12 @@
       </c>
       <c r="C1594" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F1594" t="n">
@@ -48810,7 +49520,12 @@
       </c>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="E1603" t="inlineStr">
@@ -49569,12 +50284,12 @@
       </c>
       <c r="C1629" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1629" t="inlineStr">
         <is>
-          <t>金属部分は取り外して不燃ごみへ</t>
+          <t>（古紙・布類）の【古紙（雑がみ）】金属部分は取り外して不燃ごみへ</t>
         </is>
       </c>
       <c r="F1629" t="n">
@@ -49661,7 +50376,12 @@
       </c>
       <c r="C1632" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1632" t="n">
@@ -50077,7 +50797,12 @@
       </c>
       <c r="C1646" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F1646" t="n">
@@ -50135,7 +50860,12 @@
       </c>
       <c r="C1648" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F1648" t="n">
@@ -50469,7 +51199,12 @@
       </c>
       <c r="C1659" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1659" t="n">
@@ -50619,7 +51354,12 @@
       </c>
       <c r="C1664" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F1664" t="n">
@@ -51340,7 +52080,12 @@
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E1688" t="inlineStr">
@@ -51374,7 +52119,12 @@
       </c>
       <c r="C1689" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
         </is>
       </c>
       <c r="F1689" t="n">
@@ -51819,7 +52569,12 @@
       </c>
       <c r="C1704" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F1704" t="n">
@@ -52767,7 +53522,12 @@
       </c>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1736" t="n">
@@ -53406,7 +54166,12 @@
       </c>
       <c r="C1757" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1757" t="n">
@@ -53580,7 +54345,12 @@
       </c>
       <c r="C1763" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1763" t="n">
@@ -53667,7 +54437,12 @@
       </c>
       <c r="C1766" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1766" t="n">
@@ -53904,7 +54679,12 @@
       </c>
       <c r="C1774" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1774" t="n">
@@ -54514,7 +55294,12 @@
       </c>
       <c r="C1794" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑誌）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑誌）】</t>
         </is>
       </c>
       <c r="F1794" t="n">
@@ -54862,7 +55647,12 @@
       </c>
       <c r="C1806" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1806" t="n">
@@ -55225,7 +56015,12 @@
       </c>
       <c r="C1818" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F1818" t="n">
@@ -55593,12 +56388,12 @@
       </c>
       <c r="C1830" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1830" t="inlineStr">
         <is>
-          <t>窓はそのままリサイクル可能と表記があればそのままで可</t>
+          <t>（古紙・布類）の【古紙（雑がみ）】窓はそのままリサイクル可能と表記があればそのままで可</t>
         </is>
       </c>
       <c r="F1830" t="n">
@@ -56633,7 +57428,12 @@
       </c>
       <c r="C1865" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E1865" t="inlineStr">
@@ -56667,7 +57467,12 @@
       </c>
       <c r="C1866" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【ﾍﾟｯﾄﾎﾞﾄﾙ】</t>
         </is>
       </c>
       <c r="E1866" t="inlineStr">
@@ -56730,7 +57535,12 @@
       </c>
       <c r="C1868" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="E1868" t="inlineStr">
@@ -57083,7 +57893,12 @@
       </c>
       <c r="C1880" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1880" t="n">
@@ -57228,7 +58043,12 @@
       </c>
       <c r="C1885" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1885" t="n">
@@ -57349,7 +58169,12 @@
       </c>
       <c r="C1889" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1889" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1889" t="n">
@@ -58612,12 +59437,12 @@
       </c>
       <c r="C1931" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D1931" t="inlineStr">
         <is>
-          <t>※帯などの小物類は「可燃ごみ」へ</t>
+          <t>（古紙・布類）の【布類】※帯などの小物類は「可燃ごみ」へ</t>
         </is>
       </c>
       <c r="F1931" t="n">
@@ -58849,7 +59674,12 @@
       </c>
       <c r="C1939" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F1939" t="n">
@@ -59023,7 +59853,12 @@
       </c>
       <c r="C1945" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1945" t="n">
@@ -59585,7 +60420,12 @@
       </c>
       <c r="C1963" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1963" t="n">
@@ -59643,7 +60483,12 @@
       </c>
       <c r="C1965" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1965" t="n">
@@ -59701,7 +60546,12 @@
       </c>
       <c r="C1967" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D1967" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F1967" t="n">
@@ -60852,7 +61702,12 @@
       </c>
       <c r="C2006" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2006" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F2006" t="n">
@@ -61026,7 +61881,12 @@
       </c>
       <c r="C2012" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F2012" t="n">
@@ -61336,7 +62196,12 @@
       </c>
       <c r="C2022" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2022" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F2022" t="n">
@@ -61974,7 +62839,12 @@
       </c>
       <c r="C2044" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2044" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F2044" t="n">
@@ -62032,7 +62902,12 @@
       </c>
       <c r="C2046" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2046" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【布類】</t>
         </is>
       </c>
       <c r="F2046" t="n">
@@ -62090,7 +62965,12 @@
       </c>
       <c r="C2048" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2048" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F2048" t="n">
@@ -62177,7 +63057,12 @@
       </c>
       <c r="C2051" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2051" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E2051" t="inlineStr">
@@ -62240,7 +63125,12 @@
       </c>
       <c r="C2053" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2053" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【缶】</t>
         </is>
       </c>
       <c r="F2053" t="n">
@@ -62356,7 +63246,12 @@
       </c>
       <c r="C2057" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2057" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F2057" t="n">
@@ -62443,7 +63338,12 @@
       </c>
       <c r="C2060" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2060" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="F2060" t="n">
@@ -62588,12 +63488,12 @@
       </c>
       <c r="C2065" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【布類】</t>
+          <t>資源物</t>
         </is>
       </c>
       <c r="D2065" t="inlineStr">
         <is>
-          <t>帯や足袋などの小物や反物は「可燃ごみ」へ</t>
+          <t>（古紙・布類）の【布類】帯や足袋などの小物や反物は「可燃ごみ」へ</t>
         </is>
       </c>
       <c r="F2065" t="n">
@@ -62680,7 +63580,12 @@
       </c>
       <c r="C2068" t="inlineStr">
         <is>
-          <t>資源物（古紙・布類）の【古紙（雑がみ）】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2068" t="inlineStr">
+        <is>
+          <t>（古紙・布類）の【古紙（雑がみ）】</t>
         </is>
       </c>
       <c r="E2068" t="inlineStr">
@@ -62777,7 +63682,12 @@
       </c>
       <c r="C2071" t="inlineStr">
         <is>
-          <t>資源物（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
+          <t>資源物</t>
+        </is>
+      </c>
+      <c r="D2071" t="inlineStr">
+        <is>
+          <t>（びん・缶・ﾍﾟｯﾄﾎﾞﾄﾙ）の【びん】</t>
         </is>
       </c>
       <c r="E2071" t="inlineStr">
